--- a/в бланки заводов/ПОКОМ КИ/pokom_ki/UZ/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ КИ/pokom_ki/UZ/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\UZ\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB0791E-E7FD-4C45-A4B0-0A8099398CCE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAD3FD7-7E2E-497F-82C8-71C4ACE36AC7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="278">
   <si>
     <t>SU002829</t>
   </si>
@@ -808,6 +808,66 @@
   </si>
   <si>
     <t>П/к колбасы «Мясорубская» ф/в 0,28 н/о ТМ «Стародворье»</t>
+  </si>
+  <si>
+    <t>0227 Сардельки «Стародворские с говядиной» Весовые NDX ТМ «Стародворье»  ПОКОМ</t>
+  </si>
+  <si>
+    <t>1718-Сосиски Вязанка Молочные ТМ Стародворские колбасы ТС  амицел в мод. газов.среде 0,45кг</t>
+  </si>
+  <si>
+    <t>1820-Колбаса Сервелат Зернистый ТМ Стародворье в оболочке фиброуз в вакуумной упаковке</t>
+  </si>
+  <si>
+    <t>2201 Колбаса Докторская ГОСТ ТМ Стародворье  ПОКОМ</t>
+  </si>
+  <si>
+    <t>2252 Колбаса Кракушка пряная с сальцем 0,3кг ТМ Стародворье ТС Баварушка  ПОКОМ</t>
+  </si>
+  <si>
+    <t>2367 Сардельки «Сливушки» фикс.вес 0,33 п/а мгс ТМ «Вязанка»  ПОКОМ</t>
+  </si>
+  <si>
+    <t>2606 Колбаса Сервелат Филейбургский с филе сочного окорока срез 0,35кг Баварушка  ПОКОМ</t>
+  </si>
+  <si>
+    <t>2614 Копченые колбасы «Салями Филейбургская зернистая» Весовой фиброуз ТМ «Баварушка»  ПОКОМ</t>
+  </si>
+  <si>
+    <t>2617 Колбаса Сервелат Филедворский 0,35кг ТМ Стародворье  ПОКОМ</t>
+  </si>
+  <si>
+    <t>2674 Вареные колбасы Классическая Вязанка Фикс.вес 0,6 Вектор Вязанка  ПОКОМ</t>
+  </si>
+  <si>
+    <t>2799 Сосиски Сочинки по-баварски Бавария Фикс.вес 0,4 П/а мгс Стародворье  ПОКОМ</t>
+  </si>
+  <si>
+    <t>2827 Колбаса вареная Сливушка Вязанка Фикс.вес 0,75 П/а Вязанка  ПОКОМ</t>
+  </si>
+  <si>
+    <t>3046 П/к колбасы «Мясорубская» ф/в 0,28 н/о ТМ «Стародворье»  ПОКОМ</t>
+  </si>
+  <si>
+    <t>3333 Сосиски «Ганноверские» Фикс.вес 0,5 П/а мгс ТМ «Стародворье»  ПОКОМ</t>
+  </si>
+  <si>
+    <t>3340  Сосиски «Венские» ф/в 0,6 п/а ТМ «Стародворье»  ПОКОМ</t>
+  </si>
+  <si>
+    <t>3391 Вареные колбасы «Филедворская со шпиком по-стародворски» Весовой п/а ТМ «Стародворье»  ПОКОМ</t>
+  </si>
+  <si>
+    <t>Колбаса Дугушка со шпиком ТМ Стародворье ТС Дугушка в полиамидной оболочке 0,6 кг УВК</t>
+  </si>
+  <si>
+    <t>SU002635</t>
+  </si>
+  <si>
+    <t>P004690</t>
+  </si>
+  <si>
+    <t>Вареные колбасы «Дугушка со шпиком» Фикс.вес 0,6 П/а ТМ «Дугушка»</t>
   </si>
 </sst>
 </file>
@@ -3064,13 +3124,25 @@
       <c r="J70" s="1"/>
       <c r="K70" s="20"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="6"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="5"/>
+    <row r="71" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D71" s="4">
+        <v>4301060406</v>
+      </c>
+      <c r="E71" s="3">
+        <v>4607091384482</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="G71" s="16"/>
       <c r="H71" s="1"/>
       <c r="I71" s="20"/>
@@ -3078,51 +3150,99 @@
       <c r="K71" s="20"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="6"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="5"/>
+      <c r="A72" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D72" s="4">
+        <v>4301051718</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4607091385731</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>211</v>
+      </c>
       <c r="G72" s="16"/>
       <c r="H72" s="1"/>
       <c r="I72" s="20"/>
       <c r="J72" s="1"/>
       <c r="K72" s="20"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="6"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="5"/>
+    <row r="73" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D73" s="4">
+        <v>4301030878</v>
+      </c>
+      <c r="E73" s="3">
+        <v>4607091387193</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>206</v>
+      </c>
       <c r="G73" s="16"/>
       <c r="H73" s="1"/>
       <c r="I73" s="20"/>
       <c r="J73" s="1"/>
       <c r="K73" s="20"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="6"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="5"/>
+    <row r="74" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D74" s="4">
+        <v>4301011223</v>
+      </c>
+      <c r="E74" s="3">
+        <v>4607091383423</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>202</v>
+      </c>
       <c r="G74" s="16"/>
       <c r="H74" s="1"/>
       <c r="I74" s="20"/>
       <c r="J74" s="1"/>
       <c r="K74" s="20"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="6"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="5"/>
+    <row r="75" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D75" s="4">
+        <v>4301031066</v>
+      </c>
+      <c r="E75" s="3">
+        <v>4607091383836</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>255</v>
+      </c>
       <c r="G75" s="16"/>
       <c r="H75" s="1"/>
       <c r="I75" s="20"/>
@@ -3130,90 +3250,174 @@
       <c r="K75" s="20"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="6"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="5"/>
+      <c r="A76" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D76" s="4">
+        <v>4301060317</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4680115880238</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>213</v>
+      </c>
       <c r="G76" s="16"/>
       <c r="H76" s="1"/>
       <c r="I76" s="20"/>
       <c r="J76" s="1"/>
       <c r="K76" s="20"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="6"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="5"/>
+    <row r="77" spans="1:11" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D77" s="4">
+        <v>4301031358</v>
+      </c>
+      <c r="E77" s="3">
+        <v>4607091389531</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="G77" s="16"/>
       <c r="H77" s="1"/>
       <c r="I77" s="20"/>
       <c r="J77" s="1"/>
       <c r="K77" s="20"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="6"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="5"/>
+    <row r="78" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D78" s="4">
+        <v>4301031405</v>
+      </c>
+      <c r="E78" s="3">
+        <v>4680115886100</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>214</v>
+      </c>
       <c r="G78" s="16"/>
       <c r="H78" s="1"/>
       <c r="I78" s="20"/>
       <c r="J78" s="1"/>
       <c r="K78" s="20"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="6"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="5"/>
+    <row r="79" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D79" s="4">
+        <v>4301031305</v>
+      </c>
+      <c r="E79" s="3">
+        <v>4607091389845</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>254</v>
+      </c>
       <c r="G79" s="16"/>
       <c r="H79" s="1"/>
       <c r="I79" s="20"/>
       <c r="J79" s="1"/>
       <c r="K79" s="20"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="6"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="5"/>
+    <row r="80" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A80" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D80" s="4">
+        <v>4301011386</v>
+      </c>
+      <c r="E80" s="3">
+        <v>4680115880283</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>210</v>
+      </c>
       <c r="G80" s="16"/>
       <c r="H80" s="1"/>
       <c r="I80" s="20"/>
       <c r="J80" s="1"/>
       <c r="K80" s="20"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="6"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="5"/>
+    <row r="81" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D81" s="4">
+        <v>4301051388</v>
+      </c>
+      <c r="E81" s="3">
+        <v>4680115881211</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>204</v>
+      </c>
       <c r="G81" s="16"/>
       <c r="H81" s="1"/>
       <c r="I81" s="20"/>
       <c r="J81" s="1"/>
       <c r="K81" s="20"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="6"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="5"/>
+    <row r="82" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A82" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D82" s="4">
+        <v>4301011462</v>
+      </c>
+      <c r="E82" s="3">
+        <v>4680115881457</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>212</v>
+      </c>
       <c r="G82" s="16"/>
       <c r="H82" s="1"/>
       <c r="I82" s="20"/>
@@ -3221,25 +3425,49 @@
       <c r="K82" s="20"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="6"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="5"/>
+      <c r="A83" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D83" s="4">
+        <v>4301031245</v>
+      </c>
+      <c r="E83" s="3">
+        <v>4680115883963</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>257</v>
+      </c>
       <c r="G83" s="16"/>
       <c r="H83" s="1"/>
       <c r="I83" s="20"/>
       <c r="J83" s="1"/>
       <c r="K83" s="20"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="6"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="5"/>
+    <row r="84" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D84" s="4">
+        <v>4301051734</v>
+      </c>
+      <c r="E84" s="3">
+        <v>4680115884588</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>197</v>
+      </c>
       <c r="G84" s="16"/>
       <c r="H84" s="1"/>
       <c r="I84" s="20"/>
@@ -3247,38 +3475,74 @@
       <c r="K84" s="20"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="6"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="5"/>
+      <c r="A85" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D85" s="4">
+        <v>4301051782</v>
+      </c>
+      <c r="E85" s="3">
+        <v>4680115884618</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>205</v>
+      </c>
       <c r="G85" s="16"/>
       <c r="H85" s="1"/>
       <c r="I85" s="20"/>
       <c r="J85" s="1"/>
       <c r="K85" s="20"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="6"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="5"/>
+    <row r="86" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D86" s="4">
+        <v>4301011853</v>
+      </c>
+      <c r="E86" s="3">
+        <v>4680115885851</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>203</v>
+      </c>
       <c r="G86" s="16"/>
       <c r="H86" s="1"/>
       <c r="I86" s="20"/>
       <c r="J86" s="1"/>
       <c r="K86" s="20"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="6"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="5"/>
+    <row r="87" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D87" s="4">
+        <v>4301012036</v>
+      </c>
+      <c r="E87" s="3">
+        <v>4680115882782</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>277</v>
+      </c>
       <c r="G87" s="16"/>
       <c r="H87" s="1"/>
       <c r="I87" s="20"/>
